--- a/AAII_Financials/Yearly/BOOT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/BOOT_YR_FIN.xlsx
@@ -1072,7 +1072,7 @@
         <v>100</v>
       </c>
       <c r="G15" s="3">
-        <v>35900</v>
+        <v>36800</v>
       </c>
       <c r="H15" s="3">
         <v>27400</v>
@@ -1315,7 +1315,7 @@
         <v>201700</v>
       </c>
       <c r="G21" s="3">
-        <v>267700</v>
+        <v>268600</v>
       </c>
       <c r="H21" s="3">
         <v>285700</v>
@@ -4103,7 +4103,7 @@
         <v>50300</v>
       </c>
       <c r="G83" s="3">
-        <v>35900</v>
+        <v>36800</v>
       </c>
       <c r="H83" s="3">
         <v>27300</v>
